--- a/Doc/단위테스트/_excel_upload_cases/DMF0014/15_UOM.xlsx
+++ b/Doc/단위테스트/_excel_upload_cases/DMF0014/15_UOM.xlsx
@@ -491,22 +491,22 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20261102</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20261109</t>
         </is>
       </c>
     </row>
